--- a/branches/master/StructureDefinition-funding-source.xlsx
+++ b/branches/master/StructureDefinition-funding-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-funding-source.xlsx
+++ b/branches/master/StructureDefinition-funding-source.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$48</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1823" uniqueCount="409">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -237,16 +237,19 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Mapping: HL7 v2 Mapping</t>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
+    <t>Mapping: HL7 V2 Mapping</t>
   </si>
   <si>
     <t>Mapping: RIM Mapping</t>
   </si>
   <si>
+    <t>Mapping: Interface Pattern</t>
+  </si>
+  <si>
     <t>Mapping: ServD</t>
-  </si>
-  <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
     <t/>
@@ -268,10 +271,16 @@
     <t>A formally or informally recognized grouping of people or organizations formed for the purpose of achieving some form of collective action.  Includes companies, institutions, corporations, departments, community groups, healthcare practice groups, payer/insurer, etc.</t>
   </si>
   <si>
+    <t>administrative.group</t>
+  </si>
+  <si>
     <t>(also see master files messages)</t>
   </si>
   <si>
-    <t>Organization(classCode=ORG, determinerCode=INST)</t>
+    <t>Entity, Role, or Act,Organization(classCode=ORG, determinerCode=INST)</t>
+  </si>
+  <si>
+    <t>ParticipantContactable</t>
   </si>
   <si>
     <t>Organization.id</t>
@@ -293,7 +302,7 @@
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>Within the context of the FHIR RESTful interactions, the resource has an id except for cases like the create and conditional update. Otherwise, the use of the resouce id depends on the given use case.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -332,7 +341,7 @@
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
   </si>
   <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of its narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -354,13 +363,13 @@
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>IETF language tag for a human language</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -383,10 +392,14 @@
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
   </si>
   <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>Contained resources do not have a narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-6
+</t>
   </si>
   <si>
     <t>Act.text?</t>
@@ -406,13 +419,17 @@
     <t>Contained, inline Resources</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, nor can they have their own independent transaction scope. This is allowed to be a Parameters resource if and only if it is referenced by a resource that provides context/meaning.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags in their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>dom-2
+dom-4dom-3dom-5</t>
   </si>
   <si>
     <t>N/A</t>
@@ -458,319 +475,320 @@
     <t>The index for the funding organization.</t>
   </si>
   <si>
+    <t>Organization.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Organization.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Identifies this organization  across multiple systems</t>
+  </si>
+  <si>
+    <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
+  </si>
+  <si>
+    <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>Slice based on the type of identifier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">org-1
+</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>XON.10 / XON.3</t>
+  </si>
+  <si>
+    <t>.scopes[Role](classCode=IDENT)</t>
+  </si>
+  <si>
+    <t>Participant.identifier</t>
+  </si>
+  <si>
+    <t>./Identifiers</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID</t>
+  </si>
+  <si>
+    <t>OrgID</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>Organization.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Organization.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.extension</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|5.0.0</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
 </t>
   </si>
   <si>
-    <t>Identifies this organization  across multiple systems</t>
-  </si>
-  <si>
-    <t>Identifier for the organization that is used to identify the organization across multiple disparate systems.</t>
-  </si>
-  <si>
-    <t>Organizations are known by a variety of ids. Some institutions maintain several, and most collect identifiers for exchange with other organizations concerning the organization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:system}
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
 </t>
   </si>
   <si>
-    <t>Slice based on the type of identifier.</t>
-  </si>
-  <si>
-    <t>openAtEnd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org-1
-</t>
-  </si>
-  <si>
-    <t>XON.10 / XON.3</t>
-  </si>
-  <si>
-    <t>.scopes[Role](classCode=IDENT)</t>
-  </si>
-  <si>
-    <t>./Identifiers</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID</t>
-  </si>
-  <si>
-    <t>OrgID</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.id</t>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
+  </si>
+  <si>
+    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should be an absolute reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.version</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.version</t>
   </si>
   <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Organization.identifier:OrgID.type.coding.code</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>XX</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cod-1
 </t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Organization.identifier:OrgID.type.coding.code</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>XX</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -876,7 +894,7 @@
     <t>The namespace for the identifier value</t>
   </si>
   <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>Establishes the namespace for the value - that is, an absolute URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -915,13 +933,17 @@
     <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
   </si>
   <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [http://hl7.org/fhir/StructureDefinition/rendered-value](http://hl7.org/fhir/extensions/StructureDefinition-rendered-value.html)). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>123456</t>
   </si>
   <si>
     <t>Identifier.value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ident-1
+</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -1011,16 +1033,19 @@
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
-    <t>No equivalent in HL7 v2</t>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>No equivalent in HL7 V2</t>
   </si>
   <si>
     <t>.status</t>
   </si>
   <si>
+    <t>Participant.active</t>
+  </si>
+  <si>
     <t>./Status (however this concept in ServD more covers why the organization is active or not, could be delisted, deregistered, not operational yet) this could alternatively be derived from ./StartDate and ./EndDate and given a context date.</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
   </si>
   <si>
     <t>Organization.type</t>
@@ -1049,15 +1074,15 @@
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
   </si>
   <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
     <t>No equivalent in v2</t>
   </si>
   <si>
     <t>.code</t>
   </si>
   <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>Organization.name</t>
   </si>
   <si>
@@ -1077,6 +1102,9 @@
   </si>
   <si>
     <t>.name</t>
+  </si>
+  <si>
+    <t>Participant.name</t>
   </si>
   <si>
     <t>.PreferredName/Name</t>
@@ -1098,122 +1126,107 @@
 For searching knowing previous names that the organization was known by can be very useful.</t>
   </si>
   <si>
-    <t>Organization.telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactPoint
+    <t>Organization.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">markdown
 </t>
   </si>
   <si>
-    <t>A contact detail for the organization</t>
-  </si>
-  <si>
-    <t>A contact detail for the organization.</t>
-  </si>
-  <si>
-    <t>The use code 'home' is not to be used. Note that these contacts are not the contact details of people who are employed by or represent the organization, but official contacts for the organization itself.</t>
-  </si>
-  <si>
-    <t>Human contact for the organization.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org-3
+    <t>Additional details about the Organization that could be displayed as further information to identify the Organization beyond its name</t>
+  </si>
+  <si>
+    <t>Description of the organization, which helps provide additional general context on the organization to ensure that the correct organization is selected.</t>
+  </si>
+  <si>
+    <t>Humans need additional information to verify a correct Organization has been selected.</t>
+  </si>
+  <si>
+    <t>.playingEntity[classCode=PLC determinerCode=INSTANCE].desc</t>
+  </si>
+  <si>
+    <t>Organization.contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExtendedContactDetail
 </t>
   </si>
   <si>
+    <t>Official contact details for the Organization</t>
+  </si>
+  <si>
+    <t>The contact details of communication devices available relevant to the specific Organization. This can include addresses, phone numbers, fax numbers, mobile numbers, email addresses and web sites.</t>
+  </si>
+  <si>
+    <t>The address/telecom use code 'home' are not to be used. Note that these contacts are not the contact details of people who provide the service (that would be through PractitionerRole), these are official contacts for the Organization itself for specific purposes. E.g. Mailing Addresses, Billing Addresses, Contact numbers for Booking or Billing Enquiries, general web address, web address for online bookings etc.</t>
+  </si>
+  <si>
+    <t>Need to keep track of assigned contact points within bigger organization.</t>
+  </si>
+  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
-  </si>
-  <si>
-    <t>ORC-22?</t>
-  </si>
-  <si>
-    <t>.telecom</t>
-  </si>
-  <si>
-    <t>./ContactPoints</t>
-  </si>
-  <si>
-    <t>Organization.address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Address
+org-3:The telecom of an organization can never be of use 'home' {telecom.where(use = 'home').empty()}org-4:The address of an organization can never be of use 'home' {address.where(use = 'home').empty()}</t>
+  </si>
+  <si>
+    <t>.contactParty</t>
+  </si>
+  <si>
+    <t>Organization.partOf</t>
+  </si>
+  <si>
+    <t>The organization of which this organization forms a part</t>
+  </si>
+  <si>
+    <t>The organization of which this organization forms a part.</t>
+  </si>
+  <si>
+    <t>Need to be able to track the hierarchy of organizations within an organization.</t>
+  </si>
+  <si>
+    <t>.playedBy[classCode=Part].scoper</t>
+  </si>
+  <si>
+    <t>Organization.endpoint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Endpoint)
 </t>
   </si>
   <si>
-    <t>An address for the organization</t>
-  </si>
-  <si>
-    <t>An address for the organization.</t>
-  </si>
-  <si>
-    <t>Organization may have multiple addresses with different uses or applicable periods. The use code 'home' is not to be used.</t>
-  </si>
-  <si>
-    <t>May need to keep track of the organization's addresses for contacting, billing or reporting requirements.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">org-2
-</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-org-2:An address of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
-  </si>
-  <si>
-    <t>ORC-23?</t>
-  </si>
-  <si>
-    <t>.address</t>
-  </si>
-  <si>
-    <t>./PrimaryAddress and ./OtherAddresses</t>
-  </si>
-  <si>
-    <t>Organization.partOf</t>
-  </si>
-  <si>
-    <t>The organization of which this organization forms a part</t>
-  </si>
-  <si>
-    <t>The organization of which this organization forms a part.</t>
-  </si>
-  <si>
-    <t>Need to be able to track the hierarchy of organizations within an organization.</t>
-  </si>
-  <si>
-    <t>.playedBy[classCode=Part].scoper</t>
-  </si>
-  <si>
-    <t>Organization.contact</t>
+    <t>Technical endpoints providing access to services operated for the organization</t>
+  </si>
+  <si>
+    <t>Technical endpoints providing access to services operated for the organization.</t>
+  </si>
+  <si>
+    <t>Organizations have multiple systems that provide various services and need to be able to define the technical connection details for how to connect to them, and for what purpose.</t>
+  </si>
+  <si>
+    <t>Organization.qualification</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
 </t>
   </si>
   <si>
-    <t>Contact for the organization for a certain purpose</t>
-  </si>
-  <si>
-    <t>Contact for the organization for a certain purpose.</t>
-  </si>
-  <si>
-    <t>Where multiple contacts for the same purpose are provided there is a standard extension that can be used to determine which one is the preferred contact to use.</t>
-  </si>
-  <si>
-    <t>Need to keep track of assigned contact points within bigger organization.</t>
-  </si>
-  <si>
-    <t>.contactParty</t>
-  </si>
-  <si>
-    <t>Organization.contact.id</t>
-  </si>
-  <si>
-    <t>Organization.contact.extension</t>
-  </si>
-  <si>
-    <t>Organization.contact.modifierExtension</t>
+    <t>Qualifications, certifications, accreditations, licenses, training, etc. pertaining to the provision of care</t>
+  </si>
+  <si>
+    <t>The official certifications, accreditations, training, designations and licenses that authorize and/or otherwise endorse the provision of care by the organization.++For example, an approval to provide a type of services issued by a certifying body (such as the US Joint Commission) to an organization.</t>
+  </si>
+  <si>
+    <t>CER?</t>
+  </si>
+  <si>
+    <t>Organization.qualification.id</t>
+  </si>
+  <si>
+    <t>Organization.qualification.extension</t>
+  </si>
+  <si>
+    <t>Organization.qualification.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -1223,106 +1236,56 @@
     <t>Extensions that cannot be ignored even if unrecognized</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>Organization.contact.purpose</t>
-  </si>
-  <si>
-    <t>The type of contact</t>
-  </si>
-  <si>
-    <t>Indicates a purpose for which the contact can be reached.</t>
-  </si>
-  <si>
-    <t>Need to distinguish between multiple contact persons.</t>
-  </si>
-  <si>
-    <t>The purpose for which you would contact a contact party.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
-  </si>
-  <si>
-    <t>./type</t>
-  </si>
-  <si>
-    <t>Organization.contact.name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HumanName
-</t>
-  </si>
-  <si>
-    <t>A name associated with the contact</t>
-  </si>
-  <si>
-    <t>A name associated with the contact.</t>
-  </si>
-  <si>
-    <t>Need to be able to track the person by name.</t>
-  </si>
-  <si>
-    <t>PID-5, PID-9</t>
-  </si>
-  <si>
-    <t>./name</t>
-  </si>
-  <si>
-    <t>Organization.contact.telecom</t>
-  </si>
-  <si>
-    <t>Contact details (telephone, email, etc.)  for a contact</t>
-  </si>
-  <si>
-    <t>A contact detail (e.g. a telephone number or an email address) by which the party may be contacted.</t>
-  </si>
-  <si>
-    <t>People have (primary) ways to contact them in some way such as phone, email.</t>
-  </si>
-  <si>
-    <t>PID-13, PID-14</t>
-  </si>
-  <si>
-    <t>./telecom</t>
-  </si>
-  <si>
-    <t>Organization.contact.address</t>
-  </si>
-  <si>
-    <t>Visiting or postal addresses for the contact</t>
-  </si>
-  <si>
-    <t>Visiting or postal addresses for the contact.</t>
-  </si>
-  <si>
-    <t>May need to keep track of a contact party's address for contacting, billing or reporting requirements.</t>
-  </si>
-  <si>
-    <t>PID-11</t>
-  </si>
-  <si>
-    <t>./addr</t>
-  </si>
-  <si>
-    <t>Organization.endpoint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Endpoint)
-</t>
-  </si>
-  <si>
-    <t>Technical endpoints providing access to services operated for the organization</t>
-  </si>
-  <si>
-    <t>Technical endpoints providing access to services operated for the organization.</t>
-  </si>
-  <si>
-    <t>Organizations have multiple systems that provide various services and need to be able to define the technical connection details for how to connect to them, and for what purpose.</t>
+    <t>Organization.qualification.identifier</t>
+  </si>
+  <si>
+    <t>An identifier for this qualification for the organization</t>
+  </si>
+  <si>
+    <t>An identifier allocated to this qualification for this organization.</t>
+  </si>
+  <si>
+    <t>Often, specific identities are assigned for the qualification by the assigning organization.</t>
+  </si>
+  <si>
+    <t>Organization.qualification.code</t>
+  </si>
+  <si>
+    <t>Coded representation of the qualification</t>
+  </si>
+  <si>
+    <t>Coded representation of the qualification.</t>
+  </si>
+  <si>
+    <t>Specific qualification the organization has to provide a service.</t>
+  </si>
+  <si>
+    <t>Organization.qualification.period</t>
+  </si>
+  <si>
+    <t>Period during which the qualification is valid</t>
+  </si>
+  <si>
+    <t>Period during which the qualification is valid.</t>
+  </si>
+  <si>
+    <t>Qualifications are often for a limited period of time, and can be revoked.</t>
+  </si>
+  <si>
+    <t>Organization.qualification.issuer</t>
+  </si>
+  <si>
+    <t>Organization that regulates and issues the qualification</t>
+  </si>
+  <si>
+    <t>Organization that regulates and issues the qualification.</t>
   </si>
 </sst>
 </file>
@@ -1471,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1558,77 +1521,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>
@@ -1639,7 +1610,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN48"/>
+  <dimension ref="A1:AO48"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.45703125" customWidth="true" bestFit="true"/>
@@ -1667,7 +1638,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.6484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.80859375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1677,10 +1648,11 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="45.6171875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="218.1953125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="45.6171875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="102.6171875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.29296875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="218.1953125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1804,6 +1776,9 @@
       <c r="AN1" t="s" s="1">
         <v>76</v>
       </c>
+      <c r="AO1" t="s" s="1">
+        <v>77</v>
+      </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
@@ -1814,4229 +1789,4338 @@
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF2" t="s" s="2">
         <v>30</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AN2" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AO2" t="s" s="2">
         <v>30</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO3" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO4" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO5" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="AA6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO6" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO7" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO8" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO9" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="L10" t="s" s="2">
         <v>9</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="AJ10" t="s" s="2">
-        <v>137</v>
-      </c>
       <c r="AK10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO10" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="P11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO11" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="P12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AD12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
+      </c>
+      <c r="AO12" t="s" s="2">
+        <v>166</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="P13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
+      </c>
+      <c r="AO13" t="s" s="2">
+        <v>166</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO14" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AD15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO15" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="P16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>184</v>
+        <v>113</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AA16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO16" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="P17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AA17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO17" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AD19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO19" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="P20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>213</v>
+        <v>78</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO20" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>167</v>
+        <v>91</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO21" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB22" t="s" s="2">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="AC22" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AD22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO22" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="P23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="T23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>78</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>235</v>
+        <v>78</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>240</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO24" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="P25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="T25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>250</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO25" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="P26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="T26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>253</v>
+        <v>78</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="P27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="P28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>279</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="P29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="U29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>284</v>
+        <v>78</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO29" t="s" s="2">
+        <v>291</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="U30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>77</v>
+        <v>299</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>294</v>
+        <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO30" t="s" s="2">
+        <v>302</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>303</v>
+        <v>78</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO31" t="s" s="2">
+        <v>311</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>313</v>
+        <v>78</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO32" t="s" s="2">
+        <v>321</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="P33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q33" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="R33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>332</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="P34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="Z34" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF34" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="AA34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>171</v>
+        <v>343</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>336</v>
+        <v>78</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>175</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="P35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>342</v>
+        <v>78</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>77</v>
+        <v>351</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>352</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="P36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>343</v>
+        <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO36" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="P37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>356</v>
+        <v>78</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>357</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>358</v>
+        <v>78</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>359</v>
+        <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="P38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>367</v>
+        <v>78</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>369</v>
+        <v>78</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>370</v>
+        <v>78</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>371</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO38" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="39" hidden="true">
@@ -6048,26 +6132,26 @@
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>373</v>
@@ -6080,77 +6164,80 @@
         <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>322</v>
+        <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>171</v>
-      </c>
       <c r="AN39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO39" t="s" s="2">
+        <v>175</v>
       </c>
     </row>
     <row r="40" hidden="true">
@@ -6162,23 +6249,23 @@
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>378</v>
@@ -6189,1000 +6276,1019 @@
       <c r="M40" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="N40" s="2"/>
+      <c r="O40" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="O40" t="s" s="2">
-        <v>382</v>
-      </c>
       <c r="P40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>377</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>383</v>
+        <v>78</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO40" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>167</v>
+        <v>383</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>168</v>
+        <v>384</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>169</v>
+        <v>385</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>170</v>
+        <v>382</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>171</v>
+        <v>386</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>144</v>
+        <v>78</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>131</v>
+        <v>234</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>172</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO42" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>387</v>
+        <v>148</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>388</v>
+        <v>178</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>389</v>
+        <v>179</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>390</v>
+        <v>181</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO43" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>77</v>
+        <v>390</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>191</v>
+        <v>136</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>394</v>
+        <v>152</v>
       </c>
       <c r="P44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>196</v>
+        <v>78</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>395</v>
+        <v>78</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>396</v>
+        <v>78</v>
       </c>
       <c r="AA44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>397</v>
+        <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO44" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>399</v>
+        <v>155</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="P45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>403</v>
+        <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>404</v>
+        <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>351</v>
+        <v>194</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>408</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>77</v>
+        <v>401</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="AG46" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>410</v>
+        <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO46" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>362</v>
+        <v>305</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="P47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>415</v>
+        <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>416</v>
+        <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO47" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>418</v>
+        <v>314</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>421</v>
-      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="U48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="W48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AA48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AD48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="AO48" t="s" s="2">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN48">
+  <autoFilter ref="A1:AO48">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>

--- a/branches/master/StructureDefinition-funding-source.xlsx
+++ b/branches/master/StructureDefinition-funding-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3082,7 +3082,7 @@
         <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>78</v>
@@ -3162,7 +3162,7 @@
         <v>161</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>162</v>

--- a/branches/master/StructureDefinition-funding-source.xlsx
+++ b/branches/master/StructureDefinition-funding-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-funding-source.xlsx
+++ b/branches/master/StructureDefinition-funding-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-funding-source.xlsx
+++ b/branches/master/StructureDefinition-funding-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-funding-source.xlsx
+++ b/branches/master/StructureDefinition-funding-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-funding-source.xlsx
+++ b/branches/master/StructureDefinition-funding-source.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
